--- a/Sources/Cuga-Calibration-Solution/Assets/Data/CIBMMDDTO-PMT12-CH3.xlsx
+++ b/Sources/Cuga-Calibration-Solution/Assets/Data/CIBMMDDTO-PMT12-CH3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\RiderProjects\semix\kaizhi.xuan\netcore_semix_cuga_calibration\Sources\Cuga-Calibration-Solution\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D6C18F3-5389-447B-B0BF-35FAC1243DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8786067B-76EA-4DA4-B476-3B201BA99745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{B581E037-9DD9-4DDB-9896-00045E382AAC}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B581E037-9DD9-4DDB-9896-00045E382AAC}"/>
   </bookViews>
   <sheets>
     <sheet name="CIBSheet" sheetId="1" r:id="rId1"/>
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V103"/>
+  <dimension ref="A1:V102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="19" max="19" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -5349,14 +5349,6 @@
         <v>1013.3808383233533</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A103">
-        <v>10</v>
-      </c>
-      <c r="B103">
-        <v>399.10898203592814</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
